--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_digit_manipulation.xlsx
@@ -738,7 +738,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -756,7 +756,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -780,14 +780,13 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M4" s="3" t="n"/>
@@ -803,10 +802,14 @@
 </t>
         </is>
       </c>
-      <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -818,7 +821,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -830,7 +833,7 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -842,7 +845,7 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>16</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
@@ -853,10 +856,16 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="n"/>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -870,7 +879,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5082
+</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -886,116 +900,121 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">615
+</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10920
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">619
-</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="n"/>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1014,13 +1033,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089
-</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">529
+</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2441
 </t>
         </is>
       </c>
@@ -1032,7 +1051,8 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1041,7 +1061,7 @@
 </t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">128
 </t>
@@ -1055,102 +1075,97 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">318
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">436
+</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">591
+</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">825
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1458
-</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">591
-</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1169,7 +1184,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5129
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -1181,18 +1196,19 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -1204,67 +1220,68 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">136
 </t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">837
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">7181
+</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">425
+</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">776
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>841</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1275,7 +1292,7 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
@@ -1285,7 +1302,7 @@
 </t>
         </is>
       </c>
-      <c r="W7" s="8" t="inlineStr">
+      <c r="W7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -1293,19 +1310,19 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -1324,7 +1341,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2298
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -1342,72 +1359,67 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1959
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1205
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -1419,49 +1431,49 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="X8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -1480,75 +1492,80 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t xml:space="preserve">11835
+</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6156
+          <t xml:space="preserve">676
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="n"/>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>091</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>634</t>
+          <t xml:space="preserve">631
+</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t xml:space="preserve">164
+</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
+          <t xml:space="preserve">17179190
+1
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">659
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">459
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">1738
 </t>
         </is>
       </c>
@@ -1559,46 +1576,46 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>76</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>53010</t>
+          <t xml:space="preserve">30
+</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
-</t>
+          <t>401</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1617,7 +1634,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1634,35 +1651,40 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">102
 </t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">147
@@ -1677,14 +1699,13 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1695,31 +1716,31 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1737,19 +1758,19 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10884
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1768,12 +1789,13 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t xml:space="preserve">2989
+</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1791,12 +1813,13 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>331</t>
+          <t xml:space="preserve">88
+</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1807,37 +1830,38 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">087
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4686
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>830</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -1848,62 +1872,60 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">22
+198
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">399
-</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="W11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">638
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1921,19 +1943,19 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2295
-</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">2989
+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -1943,13 +1965,13 @@
 </t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">091
-</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">130
 </t>
@@ -1957,61 +1979,61 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">945
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="R12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -2023,13 +2045,13 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -2047,18 +2069,20 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>940</t>
+          <t xml:space="preserve">850
+</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t>401</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2076,13 +2100,13 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293220
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">636
 </t>
         </is>
       </c>
@@ -2100,7 +2124,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
@@ -2112,13 +2136,13 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -2137,78 +2161,74 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9464</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">582
+</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">685
+</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">018
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2225,12 +2245,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3240
-</t>
-        </is>
-      </c>
+      <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">218
@@ -2239,7 +2254,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2251,19 +2266,19 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2273,7 +2288,12 @@
 </t>
         </is>
       </c>
-      <c r="K14" s="3" t="n"/>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53
+</t>
+        </is>
+      </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">144
@@ -2286,22 +2306,27 @@
 </t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">583
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
@@ -2311,7 +2336,7 @@
 </t>
         </is>
       </c>
-      <c r="S14" s="8" t="inlineStr">
+      <c r="S14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">181
 </t>
@@ -2319,13 +2344,13 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1719
-</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">712
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -2343,19 +2368,19 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2374,37 +2399,41 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3079
+          <t xml:space="preserve">14755
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="n"/>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -2416,37 +2445,26 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="M15" s="8" t="inlineStr">
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">138
 </t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">968
-</t>
-        </is>
-      </c>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -2461,7 +2479,7 @@
 </t>
         </is>
       </c>
-      <c r="S15" s="8" t="inlineStr">
+      <c r="S15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">169
 </t>
@@ -2469,7 +2487,7 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">3730
 </t>
         </is>
       </c>
@@ -2493,19 +2511,19 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8855
+          <t xml:space="preserve">3410
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2524,19 +2542,19 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14259
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2546,13 +2564,13 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11074
+          <t xml:space="preserve">474
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2562,83 +2580,93 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">732
 </t>
         </is>
       </c>
-      <c r="M16" s="3" t="n"/>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">694
+</t>
+        </is>
+      </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="n"/>
+          <t xml:space="preserve">5117
+18
+</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">60
+</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>234</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>881</t>
+          <t xml:space="preserve">880
+</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>324</t>
+          <t xml:space="preserve">39945
+</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>448</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1845
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>256</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>561</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -2657,25 +2685,25 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">343
 </t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">481
 </t>
         </is>
       </c>
@@ -2687,55 +2715,54 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">12
 </t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">746
-</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -2753,41 +2780,43 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">789
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>867</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>502</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -2806,19 +2835,18 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2250
-</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
+          <t xml:space="preserve">4285
+</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>91</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -2830,19 +2858,30 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">187
+</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -2851,7 +2890,7 @@
 </t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">130
 </t>
@@ -2859,29 +2898,32 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>911</t>
+          <t xml:space="preserve">920
+</t>
         </is>
       </c>
       <c r="P18" s="3" t="n"/>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -2900,28 +2942,25 @@
           <t>181</t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>260</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2939,7 +2978,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4285
+          <t xml:space="preserve">4406
 </t>
         </is>
       </c>
@@ -2955,19 +2994,19 @@
 </t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">952
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">121
 </t>
@@ -2981,13 +3020,13 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -2997,27 +3036,23 @@
 </t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">542
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">112
+7
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="n"/>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3035,48 +3070,50 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
-</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">672
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t xml:space="preserve">8105
+</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t>401</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3094,17 +3131,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4406
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">138
 </t>
@@ -3112,13 +3149,13 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">769
 </t>
         </is>
       </c>
@@ -3129,15 +3166,10 @@
         </is>
       </c>
       <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
+      <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -3147,7 +3179,7 @@
 </t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">151
 </t>
@@ -3155,24 +3187,25 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">112
+7
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="n"/>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="R20" s="8" t="inlineStr">
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">176
 </t>
@@ -3180,24 +3213,25 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -3209,19 +3243,19 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -3240,25 +3274,25 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">24617
+</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">419
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3270,11 +3304,16 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n"/>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">115
@@ -3283,7 +3322,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -3299,22 +3338,27 @@
 </t>
         </is>
       </c>
-      <c r="N21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="n"/>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">414
 </t>
         </is>
       </c>
@@ -3332,13 +3376,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -3350,24 +3394,25 @@
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3386,19 +3431,19 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
-</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">066
+</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -3410,11 +3455,11 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">134
 </t>
@@ -3422,80 +3467,74 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="n"/>
+      <c r="O22" s="3" t="n"/>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n"/>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="S22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">562
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3505,21 +3544,16 @@
 </t>
         </is>
       </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
+      <c r="X22" s="3" t="n"/>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">455
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3538,7 +3572,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">1477
 </t>
         </is>
       </c>
@@ -3548,11 +3582,14 @@
 </t>
         </is>
       </c>
-      <c r="E23" s="3" t="n"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3561,23 +3598,15 @@
 </t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>6170</t>
-        </is>
-      </c>
+      <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>33211</t>
-        </is>
-      </c>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">762
@@ -3587,25 +3616,25 @@
       <c r="M23" s="3" t="n"/>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1090
+          <t xml:space="preserve">1798
 </t>
         </is>
       </c>
@@ -3623,7 +3652,7 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>419</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
@@ -3634,30 +3663,29 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>442</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4995
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3675,8 +3703,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14779
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3687,7 +3714,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3699,15 +3726,11 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -3719,15 +3742,10 @@
 </t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3737,27 +3755,18 @@
 </t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
+      <c r="N24" s="3" t="n"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16
+111
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n"/>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3767,15 +3776,15 @@
 </t>
         </is>
       </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
+      <c r="S24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -3793,25 +3802,26 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="X24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3829,57 +3839,52 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t xml:space="preserve">226
+</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>961</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>146</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>901</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
+          <t>451</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">142
 </t>
@@ -3887,26 +3892,27 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="n"/>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>646</t>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="n"/>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t>1454</t>
         </is>
       </c>
       <c r="R25" s="3" t="n"/>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
@@ -3928,25 +3934,25 @@
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3965,13 +3971,13 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8904
-</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -3981,21 +3987,21 @@
 </t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -4012,13 +4018,14 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">81
+1198
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -4030,19 +4037,19 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">406
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -4052,7 +4059,7 @@
 </t>
         </is>
       </c>
-      <c r="R26" s="8" t="inlineStr">
+      <c r="R26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">175
 </t>
@@ -4066,7 +4073,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -4078,7 +4085,7 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -4089,19 +4096,19 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4120,13 +4127,13 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3260
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -4144,7 +4151,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -4163,12 +4170,17 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="8" t="inlineStr">
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
@@ -4176,31 +4188,31 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1950
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4212,13 +4224,13 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -4236,19 +4248,19 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4267,31 +4279,31 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2818
+          <t xml:space="preserve">2898
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">538
+          <t xml:space="preserve">418
+</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -4303,19 +4315,20 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">9799791979277
+2 8
 </t>
         </is>
       </c>
@@ -4325,7 +4338,7 @@
 </t>
         </is>
       </c>
-      <c r="M28" s="8" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">142
 </t>
@@ -4333,7 +4346,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4343,15 +4356,15 @@
 </t>
         </is>
       </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
+      <c r="P28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -4361,15 +4374,15 @@
 </t>
         </is>
       </c>
-      <c r="S28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4391,21 +4404,21 @@
 </t>
         </is>
       </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
+      <c r="X28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8308
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -4424,13 +4437,13 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23059
-</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">1999
+</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -4442,7 +4455,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4460,74 +4473,69 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">849
-</t>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>149</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
+          <t>7144</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="n"/>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="O29" s="3" t="n"/>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="S29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
-      <c r="T29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -4543,16 +4551,10 @@
 </t>
         </is>
       </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
+      <c r="X29" s="3" t="n"/>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
@@ -4576,7 +4578,8 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898
+          <t xml:space="preserve">1921
+188181
 </t>
         </is>
       </c>
@@ -4585,62 +4588,67 @@
           <t>7162</t>
         </is>
       </c>
-      <c r="E30" s="3" t="n"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">686
+</t>
+        </is>
+      </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">9661
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>45700</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">666
-</t>
+          <t>66611</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115656
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>3501</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7197
+</t>
+        </is>
+      </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">717
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t xml:space="preserve">10
+</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10562
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -4649,30 +4657,53 @@
           <t>8244</t>
         </is>
       </c>
-      <c r="S30" s="3" t="n"/>
-      <c r="T30" s="3" t="n"/>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">368883
+101
+</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9242175
+993 6
+</t>
+        </is>
+      </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="W30" s="3" t="n"/>
-      <c r="X30" s="3" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777
+1
+17
+</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">83
+</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>751</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4690,13 +4721,13 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4736,11 +4767,15 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4749,15 +4784,14 @@
 </t>
         </is>
       </c>
-      <c r="N31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1705
-</t>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">941
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -4769,7 +4803,7 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -4779,18 +4813,13 @@
 </t>
         </is>
       </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">723
-</t>
-        </is>
-      </c>
+      <c r="S31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">69
@@ -4799,31 +4828,27 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="n"/>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4841,11 +4866,11 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">215
 </t>
@@ -4859,62 +4884,68 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="n"/>
+          <t>4451</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="8" t="inlineStr">
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">170
 </t>
@@ -4926,22 +4957,21 @@
 </t>
         </is>
       </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">515
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
@@ -4958,14 +4988,20 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+710
+</t>
+        </is>
+      </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -4984,13 +5020,13 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2355
+          <t xml:space="preserve">4828
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -5000,27 +5036,27 @@
 </t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">882
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">786
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -5030,13 +5066,13 @@
 </t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">137
 </t>
@@ -5050,79 +5086,79 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">515
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">515
-</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1144
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5145,7 +5181,7 @@
 </t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
@@ -5153,7 +5189,8 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -5164,13 +5201,14 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">112179 1
+</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -5187,7 +5225,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5197,7 +5235,7 @@
 </t>
         </is>
       </c>
-      <c r="M34" s="8" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">116
 </t>
@@ -5205,53 +5243,54 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">177
+1
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7144
+</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="S34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="T34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">568
-</t>
-        </is>
-      </c>
-      <c r="U34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
+      <c r="V34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -5263,7 +5302,7 @@
 </t>
         </is>
       </c>
-      <c r="X34" s="8" t="inlineStr">
+      <c r="X34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">167
 </t>
@@ -5271,7 +5310,8 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">14
+247
 </t>
         </is>
       </c>
@@ -5296,36 +5336,36 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4828
+          <t xml:space="preserve">4928
 </t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">12150
+          <t xml:space="preserve">501
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">894
-</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
+          <t>436</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">937
+</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5343,7 +5383,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5353,7 +5393,7 @@
 </t>
         </is>
       </c>
-      <c r="M35" s="8" t="inlineStr">
+      <c r="M35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">155
 </t>
@@ -5361,13 +5401,14 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">14181
+60
 </t>
         </is>
       </c>
@@ -5377,9 +5418,9 @@
 </t>
         </is>
       </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">845
+      <c r="Q35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">457
 </t>
         </is>
       </c>
@@ -5391,13 +5432,13 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6009
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
@@ -5409,25 +5450,25 @@
       </c>
       <c r="V35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">2067
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="X35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">758
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
@@ -5456,25 +5497,25 @@
 </t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">242
 </t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">539
-</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">981
-</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">103
 </t>
@@ -5486,15 +5527,15 @@
 </t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5512,19 +5553,14 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">9180
 </t>
         </is>
       </c>
@@ -5536,7 +5572,7 @@
       </c>
       <c r="Q36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
@@ -5546,21 +5582,21 @@
 </t>
         </is>
       </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
+      <c r="S36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">551
+          <t xml:space="preserve">608
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5576,9 +5612,9 @@
 </t>
         </is>
       </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
+      <c r="X36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">661
 </t>
         </is>
       </c>
@@ -5590,7 +5626,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5609,24 +5645,22 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">658
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -5637,47 +5671,38 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">6139
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1757
-</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">702
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t xml:space="preserve">757
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1490
+          <t xml:space="preserve">44980
 </t>
         </is>
       </c>
@@ -5689,54 +5714,57 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t xml:space="preserve">581
+</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2348
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8098
+          <t xml:space="preserve">8048
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
-        </is>
-      </c>
-      <c r="Y37" s="3" t="n"/>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5755,7 +5783,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -5773,25 +5801,25 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5801,72 +5829,66 @@
 </t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="K38" s="3" t="n"/>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">899
+</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61718682
+68
+8987
+</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 8
+21 0
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
+14
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">314
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="n"/>
       <c r="V38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
@@ -5881,7 +5903,7 @@
       </c>
       <c r="X38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">731
+          <t xml:space="preserve">721
 </t>
         </is>
       </c>
@@ -5912,19 +5934,19 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3955
+          <t xml:space="preserve">583
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -5935,7 +5957,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -5946,13 +5968,12 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -5964,18 +5985,19 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>466</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>50</t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">10
+8917
 </t>
         </is>
       </c>
@@ -5984,44 +6006,45 @@
           <t>18</t>
         </is>
       </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t xml:space="preserve">116
+</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">647
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1911
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -6033,13 +6056,13 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">714
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>641</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6057,12 +6080,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>54521</t>
+          <t xml:space="preserve">5451
+</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -6084,27 +6108,27 @@
 </t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">115
 </t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3530
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6116,55 +6140,56 @@
       </c>
       <c r="M40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">3536
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">889
+</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+6
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">11
 </t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">585
 </t>
         </is>
       </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -6174,21 +6199,21 @@
 </t>
         </is>
       </c>
-      <c r="W40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
+      <c r="W40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -6231,31 +6256,31 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="J41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -6271,21 +6296,21 @@
 </t>
         </is>
       </c>
-      <c r="M41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">389
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">87701
 </t>
         </is>
       </c>
@@ -6295,21 +6320,21 @@
 </t>
         </is>
       </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="R41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
+      <c r="Q41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">382
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6325,15 +6350,15 @@
 </t>
         </is>
       </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="W41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">6585
 </t>
         </is>
       </c>
@@ -6374,15 +6399,16 @@
 </t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+181
 </t>
         </is>
       </c>
@@ -6392,13 +6418,13 @@
 </t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">137
 </t>
@@ -6410,40 +6436,46 @@
 </t>
         </is>
       </c>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="L42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6211
-</t>
-        </is>
-      </c>
-      <c r="M42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="n"/>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2924
+991
+</t>
+        </is>
+      </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 111
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -6453,9 +6485,9 @@
 </t>
         </is>
       </c>
-      <c r="R42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">671
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -6467,43 +6499,43 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">537
 </t>
         </is>
       </c>
@@ -6522,144 +6554,145 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53109
-</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">392
-</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
+          <t xml:space="preserve">570
+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8070
+</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">008
+</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="N43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9271
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">588
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="M43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="N43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="W43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -6678,145 +6711,143 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8571
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">634
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">610
+</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="N44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">409
+</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+1272971
+</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="T44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595
+</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">836
-</t>
-        </is>
-      </c>
-      <c r="M44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">896
-</t>
-        </is>
-      </c>
-      <c r="N44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">408
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1595
-</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="X44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7240
-</t>
+          <t>664</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -6835,89 +6866,86 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2283
+          <t xml:space="preserve">2830
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">610
+</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">708
+</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2152
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">11
 </t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6210
-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">708
-</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8985
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8511
+          <t xml:space="preserve">8871
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5409
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="n"/>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
@@ -6928,19 +6956,19 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9756
+          <t xml:space="preserve">9792
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35611
+          <t xml:space="preserve">3511
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -6952,22 +6980,28 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">92926
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>1668</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="n"/>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6989,23 +7023,19 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+4236
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">103
 </t>
@@ -7029,28 +7059,27 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="n"/>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -7066,9 +7095,9 @@
 </t>
         </is>
       </c>
-      <c r="R46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">718
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -7080,25 +7109,20 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="n"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -7110,7 +7134,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5823
+          <t xml:space="preserve">5829
 </t>
         </is>
       </c>
@@ -753,7 +753,12 @@
 </t>
         </is>
       </c>
-      <c r="F4" s="3" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">115
@@ -762,25 +767,54 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="n"/>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -801,12 +835,26 @@
 </t>
         </is>
       </c>
-      <c r="T4" s="3" t="n"/>
-      <c r="U4" s="3" t="n"/>
-      <c r="V4" s="3" t="n"/>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1520
+</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1207
+</t>
+        </is>
+      </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -828,27 +876,37 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3888
-</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n"/>
+          <t xml:space="preserve">2889
+</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
-</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n"/>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -860,26 +918,61 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="n"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="n"/>
-      <c r="R5" s="3" t="n"/>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -901,7 +994,7 @@
 </t>
         </is>
       </c>
-      <c r="W5" s="8" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">176
 </t>
@@ -913,7 +1006,12 @@
 </t>
         </is>
       </c>
-      <c r="Y5" s="3" t="n"/>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">755
+</t>
+        </is>
+      </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">60
@@ -935,45 +1033,106 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25089
-</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>136</t>
+          <t xml:space="preserve">5089
+</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">130
 </t>
         </is>
       </c>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="n"/>
-      <c r="Q6" s="3" t="n"/>
-      <c r="R6" s="3" t="n"/>
-      <c r="S6" s="3" t="n"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">619
@@ -988,24 +1147,34 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr">
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="n"/>
-      <c r="Z6" s="3" t="n"/>
+      <c r="X6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -1025,82 +1194,139 @@
 </t>
         </is>
       </c>
-      <c r="D7" s="3" t="n"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">132
 </t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1898
+</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="n"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>410</t>
+          <t xml:space="preserve">5930
+</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="n"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">591
+</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="Q7" s="3" t="n"/>
-      <c r="R7" s="3" t="n"/>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">591
-</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1918
-</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="n"/>
-      <c r="W7" s="3" t="inlineStr">
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
         </is>
       </c>
-      <c r="X7" s="3" t="n"/>
-      <c r="Y7" s="3" t="n"/>
-      <c r="Z7" s="3" t="n"/>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -1120,10 +1346,15 @@
 </t>
         </is>
       </c>
-      <c r="D8" s="3" t="n"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">419
+</t>
+        </is>
+      </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -1139,7 +1370,12 @@
 </t>
         </is>
       </c>
-      <c r="H8" s="3" t="n"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">18
@@ -1154,7 +1390,8 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t xml:space="preserve">272
+</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1169,26 +1406,51 @@
 </t>
         </is>
       </c>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">08
 </t>
         </is>
       </c>
-      <c r="Q8" s="3" t="n"/>
-      <c r="R8" s="3" t="n"/>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="n"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1198,7 +1460,12 @@
 </t>
         </is>
       </c>
-      <c r="W8" s="3" t="n"/>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
       <c r="X8" s="3" t="n"/>
       <c r="Y8" s="3" t="n"/>
       <c r="Z8" s="3" t="n"/>
@@ -1229,7 +1496,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">676
+          <t xml:space="preserve">616
 </t>
         </is>
       </c>
@@ -1241,37 +1508,55 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t xml:space="preserve">8815
+</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n"/>
+          <t xml:space="preserve">651
+</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
-</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">607
+</t>
+        </is>
+      </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">860
+</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4590
+          <t xml:space="preserve">9590
 </t>
         </is>
       </c>
@@ -1283,38 +1568,64 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11140
+          <t xml:space="preserve">11940
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="n"/>
-      <c r="T9" s="3" t="n"/>
-      <c r="U9" s="3" t="n"/>
+          <t xml:space="preserve">881
+</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">068
+</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21626
+</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="n"/>
+          <t xml:space="preserve">9590
+</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0098
+</t>
+        </is>
+      </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="n"/>
+          <t xml:space="preserve">4198
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1328,65 +1639,142 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4490
+</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4590
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3" t="n"/>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">858
+</t>
+        </is>
+      </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n"/>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">629
+</t>
+        </is>
+      </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t xml:space="preserve">106
+</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="W10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4150
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1405,94 +1793,119 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94450
+          <t xml:space="preserve">2218
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n"/>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n"/>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="n"/>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="P11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="n"/>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="S11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">106
 </t>
         </is>
       </c>
-      <c r="V11" s="8" t="inlineStr">
+      <c r="V11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
@@ -1532,96 +1945,148 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2918
-</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n"/>
+          <t xml:space="preserve">2290
+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n"/>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n"/>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="n"/>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">835
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">745
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="n"/>
-      <c r="X12" s="3" t="n"/>
-      <c r="Y12" s="3" t="n"/>
-      <c r="Z12" s="3" t="n"/>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2408
+</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1635,61 +2100,109 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3220
+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
+          <t>281</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="n"/>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">945
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="n"/>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="n"/>
-      <c r="R13" s="3" t="n"/>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">905
 </t>
         </is>
       </c>
@@ -1701,29 +2214,34 @@
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1737,15 +2255,45 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3240
+</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -1755,49 +2303,99 @@
 </t>
         </is>
       </c>
-      <c r="K14" s="3" t="n"/>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="n"/>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="n"/>
-      <c r="R14" s="3" t="n"/>
-      <c r="S14" s="3" t="n"/>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3" t="n"/>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="n"/>
+          <t xml:space="preserve">719
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">875
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1814,67 +2412,140 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3079
+</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>783</t>
+        </is>
+      </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">59
+</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="n"/>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">968
+</t>
+        </is>
+      </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="n"/>
-      <c r="R15" s="3" t="n"/>
-      <c r="S15" s="3" t="n"/>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
-</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="n"/>
-      <c r="V15" s="3" t="n"/>
+          <t xml:space="preserve">730
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="n"/>
-      <c r="Y15" s="3" t="n"/>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1891,75 +2562,148 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19722
+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">911
+</t>
+        </is>
+      </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
+          <t xml:space="preserve">474
+</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6494
+</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">59
+</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
+          <t xml:space="preserve">468
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1912
+</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">694
+</t>
+        </is>
+      </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>11642</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">648
+</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">969
 </t>
         </is>
       </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="n"/>
-      <c r="R16" s="3" t="n"/>
-      <c r="S16" s="3" t="n"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">838
+</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">884
+</t>
+        </is>
+      </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="n"/>
+          <t xml:space="preserve">1648
+</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">845
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="n"/>
+          <t xml:space="preserve">1806
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">851
+</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="Z16" s="3" t="n"/>
+          <t xml:space="preserve">4888
+</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1975,48 +2719,49 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19722
-</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">674
-</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">474
+          <t xml:space="preserve">2250
+</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">418
+</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>691</t>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -2027,81 +2772,91 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="M17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">694
-</t>
-        </is>
-      </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t>164646</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="n"/>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">929
+</t>
+        </is>
+      </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">962
-</t>
-        </is>
-      </c>
-      <c r="R17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
-</t>
-        </is>
-      </c>
-      <c r="S17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7186
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24208
+          <t xml:space="preserve">901
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -2120,76 +2875,118 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2250
-</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">4288
+</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="n"/>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>346</t>
+          <t xml:space="preserve">140
+</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="n"/>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="n"/>
-      <c r="Q18" s="3" t="n"/>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">789
-</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="n"/>
+          <t xml:space="preserve">691
+</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">169
@@ -2198,12 +2995,22 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="X18" s="3" t="n"/>
-      <c r="Y18" s="3" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">20
@@ -2225,79 +3032,130 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4285
+          <t xml:space="preserve">8406
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="n"/>
-      <c r="S19" s="3" t="n"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1691
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">540
+</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="n"/>
-      <c r="W19" s="3" t="n"/>
-      <c r="X19" s="3" t="n"/>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">810
@@ -2306,7 +3164,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -2325,73 +3183,148 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24406
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3" t="n"/>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3" t="n"/>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768
+</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">920
 </t>
         </is>
       </c>
-      <c r="P20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="n"/>
-      <c r="R20" s="3" t="n"/>
-      <c r="S20" s="3" t="n"/>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">599
-</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="n"/>
-      <c r="W20" s="3" t="n"/>
-      <c r="X20" s="3" t="n"/>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2407,68 +3340,148 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">2617
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">419
+</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n"/>
-      <c r="Q21" s="3" t="n"/>
-      <c r="R21" s="3" t="n"/>
-      <c r="S21" s="3" t="n"/>
+          <t xml:space="preserve">908
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="n"/>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="n"/>
-      <c r="X21" s="3" t="n"/>
+          <t xml:space="preserve">740
+</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 8
+</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="n"/>
+          <t xml:space="preserve">8809
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2484,85 +3497,145 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12617
-</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="n"/>
+          <t xml:space="preserve">1233
+</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1206
+</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">944
+</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="n"/>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n"/>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="n"/>
-      <c r="S22" s="3" t="inlineStr">
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">740
+</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">740
-</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="V22" s="3" t="n"/>
-      <c r="W22" s="3" t="n"/>
-      <c r="X22" s="3" t="n"/>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8709
+          <t xml:space="preserve">945
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2581,100 +3654,144 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">19212
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
-</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n"/>
+          <t xml:space="preserve">111531
+</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">494
+</t>
+        </is>
+      </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="n"/>
+          <t xml:space="preserve">9408
+</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">431
+</t>
+        </is>
+      </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">934
+          <t xml:space="preserve">698
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="n"/>
+          <t xml:space="preserve">808
+</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
+          <t xml:space="preserve">382
+</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1221
+</t>
+        </is>
+      </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">8164
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>649</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="n"/>
+          <t xml:space="preserve">1090
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">888
+</t>
+        </is>
+      </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
+          <t xml:space="preserve">3479
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="n"/>
-      <c r="W23" s="3" t="n"/>
-      <c r="X23" s="3" t="n"/>
+          <t xml:space="preserve">406
+</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9189
+</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">899
+</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9118
+</t>
+        </is>
+      </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">484
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
@@ -2693,133 +3810,145 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19832
-</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">2154
+</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">437
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t xml:space="preserve">698
+</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">382
+</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">924
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">695
+</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">871
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">28
 </t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>3321</t>
-        </is>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71621
-</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="N24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04618
-</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="n"/>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">090
-</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">888
-</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="T24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3479
-</t>
-        </is>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t>4064</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t>1984</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -2837,91 +3966,142 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2354
-</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="n"/>
+          <t xml:space="preserve">4904
+</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8492
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9108
+</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">019
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">689
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="W25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">129
 </t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="n"/>
-      <c r="Q25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
+      <c r="X25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="T25" s="3" t="n"/>
-      <c r="U25" s="3" t="n"/>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="n"/>
-      <c r="X25" s="3" t="n"/>
-      <c r="Y25" s="3" t="n"/>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">28
@@ -2943,88 +4123,148 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4904
+          <t xml:space="preserve">2878
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n"/>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="n"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 5
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">846
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">730
+</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">129
 </t>
         </is>
       </c>
-      <c r="I26" s="3" t="n"/>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="n"/>
-      <c r="S26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="n"/>
-      <c r="U26" s="3" t="n"/>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="n"/>
-      <c r="Y26" s="3" t="n"/>
-      <c r="Z26" s="3" t="n"/>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="X26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">885
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -3038,79 +4278,150 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23059
+</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="n"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">846
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="n"/>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">20
 </t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="n"/>
-      <c r="R27" s="3" t="n"/>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1730
-</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="n"/>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="n"/>
-      <c r="X27" s="3" t="n"/>
-      <c r="Y27" s="3" t="n"/>
-      <c r="Z27" s="3" t="n"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -3124,80 +4435,148 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20239
+</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1179
+</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="n"/>
-      <c r="M28" s="3" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">654
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="n"/>
-      <c r="R28" s="3" t="n"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="n"/>
-      <c r="V28" s="3" t="n"/>
-      <c r="W28" s="3" t="n"/>
-      <c r="X28" s="3" t="n"/>
-      <c r="Y28" s="3" t="n"/>
-      <c r="Z28" s="3" t="n"/>
+          <t xml:space="preserve">728
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">838
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -3213,27 +4592,37 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3059
-</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
+          <t xml:space="preserve">2898
+</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -3243,43 +4632,108 @@
 </t>
         </is>
       </c>
-      <c r="J29" s="3" t="n"/>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1950
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="n"/>
-      <c r="Q29" s="3" t="n"/>
-      <c r="R29" s="3" t="n"/>
-      <c r="S29" s="3" t="n"/>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="n"/>
-      <c r="V29" s="3" t="n"/>
-      <c r="W29" s="3" t="n"/>
-      <c r="X29" s="3" t="n"/>
-      <c r="Y29" s="3" t="n"/>
-      <c r="Z29" s="3" t="n"/>
+          <t xml:space="preserve">700
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -3295,83 +4749,146 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898
+          <t xml:space="preserve">16829
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
-</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
+          <t xml:space="preserve">11209
+</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">006
+</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">437
+</t>
+        </is>
+      </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">806
+</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">656
+</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>4566</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200214
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">874
+</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">901
+</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5619
+</t>
+        </is>
+      </c>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3946
+</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="n"/>
-      <c r="Q30" s="3" t="n"/>
-      <c r="R30" s="3" t="n"/>
-      <c r="S30" s="3" t="n"/>
-      <c r="T30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="U30" s="3" t="n"/>
-      <c r="V30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="W30" s="3" t="n"/>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1822009
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="3" t="n"/>
-      <c r="Z30" s="3" t="n"/>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4418
+</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3387,125 +4904,145 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16099
-</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">3220
+</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>360</t>
+          <t xml:space="preserve">137
+</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">88
+</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
-</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="n"/>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="3" t="n"/>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>420344</t>
+          <t xml:space="preserve">941
+</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Q31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">054
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3611
-</t>
-        </is>
-      </c>
-      <c r="U31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">346
-</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">888
 </t>
         </is>
       </c>
-      <c r="W31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">811
-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">882
-</t>
-        </is>
-      </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">94910
-</t>
-        </is>
-      </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -3523,97 +5060,148 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n"/>
+          <t xml:space="preserve">4828
+</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">88
 </t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n"/>
-      <c r="M32" s="3" t="n"/>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8950
+</t>
+        </is>
+      </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">110
 </t>
         </is>
       </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="n"/>
-      <c r="T32" s="3" t="n"/>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">810
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9011
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="n"/>
-      <c r="Y32" s="3" t="n"/>
-      <c r="Z32" s="3" t="n"/>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="W32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3627,96 +5215,145 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4828
+</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">897
+</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">930
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="n"/>
-      <c r="Q33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>1581</t>
-        </is>
-      </c>
-      <c r="S33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="n"/>
-      <c r="W33" s="3" t="n"/>
-      <c r="X33" s="3" t="n"/>
+          <t xml:space="preserve">319
+</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">834
+</t>
+        </is>
+      </c>
+      <c r="X33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">406
+</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1950
+          <t xml:space="preserve">718
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -3733,77 +5370,147 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4928
+</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
-</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="n"/>
+          <t xml:space="preserve">083
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
-</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="n"/>
-      <c r="L34" s="3" t="n"/>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="3" t="n"/>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">080
+</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="n"/>
-      <c r="Q34" s="3" t="n"/>
-      <c r="R34" s="3" t="n"/>
-      <c r="S34" s="3" t="n"/>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
-</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="V34" s="3" t="n"/>
-      <c r="W34" s="3" t="n"/>
-      <c r="X34" s="3" t="n"/>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
@@ -3820,33 +5527,47 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">740
+</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="n"/>
+          <t xml:space="preserve">894
+</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">40
@@ -3859,33 +5580,92 @@
 </t>
         </is>
       </c>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="n"/>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="M35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n"/>
-      <c r="Q35" s="3" t="n"/>
-      <c r="R35" s="3" t="n"/>
-      <c r="S35" s="3" t="n"/>
+          <t xml:space="preserve">91800
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="Q35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="n"/>
-      <c r="V35" s="3" t="n"/>
-      <c r="W35" s="3" t="n"/>
-      <c r="X35" s="3" t="n"/>
-      <c r="Y35" s="3" t="n"/>
+          <t xml:space="preserve">6008
+</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14248
+</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="X35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">755
+</t>
+        </is>
+      </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -3902,12 +5682,27 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4983
+</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -3917,8 +5712,17 @@
 </t>
         </is>
       </c>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="n"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">40
@@ -3927,44 +5731,94 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="n"/>
-      <c r="M36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">086
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="n"/>
-      <c r="O36" s="3" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">16
 </t>
         </is>
       </c>
-      <c r="Q36" s="3" t="n"/>
-      <c r="R36" s="3" t="n"/>
-      <c r="S36" s="3" t="n"/>
+      <c r="Q36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1242
+</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710
+</t>
+        </is>
+      </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
-        </is>
-      </c>
-      <c r="U36" s="3" t="n"/>
+          <t xml:space="preserve">5521
+</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14248
+</t>
+        </is>
+      </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="W36" s="3" t="n"/>
-      <c r="X36" s="3" t="n"/>
-      <c r="Y36" s="3" t="n"/>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">798
+</t>
+        </is>
+      </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">45
@@ -3986,106 +5840,139 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11828
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n"/>
+          <t xml:space="preserve">1242
+</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8258
+</t>
+        </is>
+      </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9286
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="n"/>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">040
+</t>
+        </is>
+      </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="n"/>
-      <c r="K37" s="3" t="n"/>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+</t>
+        </is>
+      </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">291
+</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="n"/>
+          <t xml:space="preserve">80120
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94490
+          <t xml:space="preserve">4490
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="Q37" s="3" t="n"/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2848
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3124
+          <t xml:space="preserve">3134
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12910
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>504</t>
+          <t xml:space="preserve">809
+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9092
+          <t xml:space="preserve">9402
 </t>
         </is>
       </c>
@@ -4114,17 +6001,32 @@
 </t>
         </is>
       </c>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3" t="n"/>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -4136,14 +6038,20 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n"/>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>454</t>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -4152,10 +6060,15 @@
 </t>
         </is>
       </c>
-      <c r="N38" s="3" t="n"/>
+      <c r="N38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">521
+</t>
+        </is>
+      </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
@@ -4165,16 +6078,36 @@
 </t>
         </is>
       </c>
-      <c r="Q38" s="3" t="n"/>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="n"/>
-      <c r="T38" s="3" t="n"/>
-      <c r="U38" s="3" t="n"/>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">621
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
@@ -4183,12 +6116,28 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>4641</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="n"/>
-      <c r="Y38" s="3" t="n"/>
-      <c r="Z38" s="3" t="n"/>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2249
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 0
+</t>
+        </is>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -4204,93 +6153,148 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13953
-</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
+          <t xml:space="preserve">3950
+</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">645
+</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="N39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">521
+</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">120
 </t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="T39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">528
+</t>
+        </is>
+      </c>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710
+</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="n"/>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n"/>
-      <c r="M39" s="3" t="n"/>
-      <c r="N39" s="3" t="n"/>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="n"/>
-      <c r="R39" s="3" t="n"/>
-      <c r="S39" s="3" t="n"/>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5208
-</t>
-        </is>
-      </c>
-      <c r="U39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="W39" s="3" t="n"/>
-      <c r="X39" s="3" t="n"/>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">718
-</t>
-        </is>
-      </c>
-      <c r="Z39" s="3" t="n"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -4306,64 +6310,140 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>40344</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
+          <t xml:space="preserve">29421
+</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">191
 </t>
         </is>
       </c>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="n"/>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="3" t="n"/>
-      <c r="N40" s="3" t="n"/>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="n"/>
-      <c r="Q40" s="3" t="n"/>
-      <c r="R40" s="3" t="n"/>
-      <c r="S40" s="3" t="n"/>
-      <c r="T40" s="3" t="n"/>
-      <c r="U40" s="8" t="inlineStr">
+          <t xml:space="preserve">2995
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">685
+</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">120
 </t>
         </is>
       </c>
-      <c r="V40" s="8" t="inlineStr">
+      <c r="V40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
 </t>
         </is>
       </c>
-      <c r="W40" s="3" t="n"/>
-      <c r="X40" s="3" t="n"/>
-      <c r="Y40" s="3" t="n"/>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">720
+</t>
+        </is>
+      </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4382,44 +6462,74 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3401
-</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">4084
+</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="n"/>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -4429,38 +6539,62 @@
 </t>
         </is>
       </c>
-      <c r="Q41" s="3" t="n"/>
-      <c r="R41" s="3" t="n"/>
-      <c r="S41" s="3" t="n"/>
-      <c r="T41" s="3" t="n"/>
+      <c r="Q41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1239
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1625
+</t>
+        </is>
+      </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="n"/>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="W41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">720
+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -4479,63 +6613,114 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13370
-</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n"/>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="n"/>
+          <t xml:space="preserve">3491
+</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="G42" s="3" t="n"/>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">40
 </t>
         </is>
       </c>
-      <c r="K42" s="3" t="n"/>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">889
+</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">434
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14605
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">104
 </t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="n"/>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="n"/>
-      <c r="R42" s="3" t="n"/>
-      <c r="S42" s="3" t="n"/>
-      <c r="T42" s="3" t="n"/>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t>1424</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="n"/>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -4545,13 +6730,13 @@
       <c r="X42" s="3" t="n"/>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">987
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4570,85 +6755,136 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16531
-</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n"/>
+          <t xml:space="preserve">5170
+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="n"/>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n"/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="n"/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="n"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="n"/>
-      <c r="Q43" s="3" t="n"/>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="R43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9593
-</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="n"/>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
+          <t xml:space="preserve">520
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
@@ -4667,17 +6903,22 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228301
-</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">917
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n"/>
+          <t xml:space="preserve">6531
+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
@@ -4685,8 +6926,18 @@
         </is>
       </c>
       <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">50
@@ -4701,7 +6952,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -4718,57 +6969,47 @@
 </t>
         </is>
       </c>
-      <c r="P44" s="3" t="n"/>
-      <c r="Q44" s="3" t="n"/>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="R44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">681
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9593
-</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="n"/>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">958
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">996
-</t>
-        </is>
-      </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">780
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">595
+</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="n"/>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="n"/>
+      <c r="X44" s="3" t="n"/>
+      <c r="Y44" s="3" t="n"/>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4784,68 +7025,118 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228301
+          <t xml:space="preserve">22830
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917
-</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
+          <t xml:space="preserve">1985
+</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2191
+</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">1288
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="n"/>
-      <c r="M45" s="3" t="n"/>
-      <c r="N45" s="3" t="n"/>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">825
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409
-</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="n"/>
-      <c r="Q45" s="3" t="n"/>
-      <c r="R45" s="3" t="n"/>
+          <t xml:space="preserve">2909
+</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1216
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1041
+</t>
+        </is>
+      </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
-</t>
-        </is>
-      </c>
-      <c r="T45" s="3" t="n"/>
-      <c r="U45" s="3" t="n"/>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3810
+</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1690
+</t>
+        </is>
+      </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1118
@@ -4854,20 +7145,24 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
+          <t xml:space="preserve">2208
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="3" t="n"/>
+          <t xml:space="preserve">896
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>46484</t>
+        </is>
+      </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -4886,11 +7181,11 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294970
-</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
+          <t xml:space="preserve">4980
+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">236
 </t>
@@ -4898,7 +7193,8 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">133
+</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -4907,13 +7203,13 @@
 </t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">118
 </t>
@@ -4921,32 +7217,58 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="N46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">389
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2541
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="n"/>
-      <c r="N46" s="3" t="n"/>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="n"/>
       <c r="R46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">171
@@ -4959,22 +7281,48 @@
 </t>
         </is>
       </c>
-      <c r="T46" s="3" t="n"/>
-      <c r="U46" s="3" t="n"/>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">585
+</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>2126</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="W46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">159
 </t>
         </is>
       </c>
-      <c r="X46" s="3" t="n"/>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+      <c r="X46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">878
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,14 +737,13 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5829
+          <t xml:space="preserve">5822
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -773,17 +772,19 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">92
+</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -801,7 +802,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -837,24 +838,20 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1520
-</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">520
+</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10 7 1
 </t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -876,13 +873,13 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2889
+          <t xml:space="preserve">3885
 </t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -904,9 +901,9 @@
 </t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -918,14 +915,13 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -936,13 +932,13 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -954,7 +950,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -1008,7 +1004,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">755
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -1049,9 +1045,9 @@
 </t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -1085,21 +1081,21 @@
 </t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">138
 </t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -1117,7 +1113,7 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -1151,15 +1147,15 @@
 </t>
         </is>
       </c>
-      <c r="W6" s="8" t="inlineStr">
+      <c r="W6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="X6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -1171,7 +1167,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1200,15 +1196,10 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1898
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -1218,7 +1209,7 @@
 </t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">120
 </t>
@@ -1226,19 +1217,19 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1248,28 +1239,27 @@
 </t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5930
+          <t xml:space="preserve">2930
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="Q7" s="3" t="n"/>
@@ -1281,7 +1271,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1291,7 +1281,7 @@
 </t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">118
 </t>
@@ -1303,7 +1293,7 @@
 </t>
         </is>
       </c>
-      <c r="W7" s="8" t="inlineStr">
+      <c r="W7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
@@ -1317,13 +1307,13 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -1348,7 +1338,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">419
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1390,8 +1380,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1408,13 +1397,13 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -1436,7 +1425,7 @@
 </t>
         </is>
       </c>
-      <c r="S8" s="8" t="inlineStr">
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">181
 </t>
@@ -1450,7 +1439,7 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
@@ -1496,7 +1485,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
+          <t xml:space="preserve">656
 </t>
         </is>
       </c>
@@ -1508,56 +1497,49 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8815
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">651
-</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">631
+</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">511
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">734
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">607
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9590
-</t>
+          <t>15901</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1568,7 +1550,7 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11940
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
@@ -1580,13 +1562,13 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">068
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21626
+          <t xml:space="preserve">2126
 </t>
         </is>
       </c>
@@ -1598,13 +1580,13 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9590
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0098
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
@@ -1616,7 +1598,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4198
+          <t xml:space="preserve">8481
 </t>
         </is>
       </c>
@@ -1641,7 +1623,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490
+          <t xml:space="preserve">4950
 </t>
         </is>
       </c>
@@ -1657,7 +1639,7 @@
 </t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
@@ -1677,17 +1659,22 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">147
@@ -1708,19 +1695,19 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">9218
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">11 3 8
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -1730,15 +1717,15 @@
 </t>
         </is>
       </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">782
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -1793,8 +1780,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2218
-</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1805,11 +1791,11 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">181
 </t>
@@ -1823,13 +1809,13 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1839,9 +1825,9 @@
 </t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -1853,41 +1839,40 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
+          <t>8850</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
@@ -1895,7 +1880,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -1969,7 +1954,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
@@ -1999,13 +1984,13 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">385
 </t>
         </is>
       </c>
@@ -2017,7 +2002,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2059,7 +2044,7 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2077,7 +2062,7 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -2118,20 +2103,21 @@
 </t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -2155,7 +2141,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -2179,7 +2165,8 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>001</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="Q13" s="8" t="inlineStr">
@@ -2196,13 +2183,13 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -2226,13 +2213,13 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -2267,7 +2254,7 @@
 </t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">134
 </t>
@@ -2275,8 +2262,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -2287,25 +2273,24 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
@@ -2323,8 +2308,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2341,8 +2325,7 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
@@ -2353,13 +2336,13 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">715
 </t>
         </is>
       </c>
@@ -2371,7 +2354,7 @@
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2427,12 +2410,12 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -2450,7 +2433,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">18 2
 </t>
         </is>
       </c>
@@ -2468,7 +2451,8 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -2485,7 +2469,7 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -2564,7 +2548,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19722
+          <t xml:space="preserve">19732
 </t>
         </is>
       </c>
@@ -2576,30 +2560,30 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>274</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">474
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6494
+          <t xml:space="preserve">644
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2611,13 +2595,13 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">460
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912
+          <t xml:space="preserve">732
 </t>
         </is>
       </c>
@@ -2629,43 +2613,39 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>11642</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">069
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
+          <t>614</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1648
-</t>
+          <t>39452</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
@@ -2676,13 +2656,13 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2694,7 +2674,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4888
+          <t xml:space="preserve">4288
 </t>
         </is>
       </c>
@@ -2719,8 +2699,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2250
-</t>
+          <t>14694</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2731,18 +2710,18 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418
-</t>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
@@ -2758,7 +2737,7 @@
 </t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
 </t>
@@ -2766,7 +2745,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">460
 </t>
         </is>
       </c>
@@ -2784,31 +2763,31 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">929
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -2820,13 +2799,13 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">789
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -2881,13 +2860,13 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2899,8 +2878,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -2911,7 +2889,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2923,85 +2901,84 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">691
+</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">80
 </t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">691
-</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="X18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -3032,13 +3009,14 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8406
+          <t xml:space="preserve">4406
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -3055,11 +3033,11 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">121
 </t>
@@ -3067,8 +3045,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -3097,8 +3074,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>464</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -3115,7 +3091,7 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -3137,22 +3113,26 @@
 </t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
+      <c r="U19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="V19" s="3" t="n"/>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="X19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1853
 </t>
         </is>
       </c>
@@ -3164,7 +3144,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">1274
 </t>
         </is>
       </c>
@@ -3189,7 +3169,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -3201,13 +3181,13 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -3219,7 +3199,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3267,44 +3247,43 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">876
+</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768
+</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">176
 </t>
         </is>
       </c>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768
-</t>
-        </is>
-      </c>
-      <c r="U20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>755</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
@@ -3358,31 +3337,31 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">419
-</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3392,9 +3371,9 @@
 </t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">562
 </t>
         </is>
       </c>
@@ -3406,8 +3385,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3422,9 +3400,9 @@
 </t>
         </is>
       </c>
-      <c r="Q21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -3436,8 +3414,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>0431</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
@@ -3448,11 +3425,11 @@
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 8
-</t>
-        </is>
-      </c>
-      <c r="V21" s="3" t="inlineStr">
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">182
 </t>
@@ -3501,15 +3478,15 @@
 </t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1206
-</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">944
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3521,11 +3498,11 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">134
 </t>
@@ -3539,7 +3516,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3551,7 +3528,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -3561,15 +3538,15 @@
 </t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3599,7 +3576,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
+          <t xml:space="preserve">7408
 </t>
         </is>
       </c>
@@ -3611,7 +3588,7 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -3635,7 +3612,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3654,38 +3631,35 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19212
-</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111531
+          <t xml:space="preserve">1131
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">494
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9408
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">431
-</t>
+          <t>26540</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
-</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3696,7 +3670,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -3708,25 +3682,24 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">1614
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8164
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3743,13 +3716,12 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -3767,32 +3739,30 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9189
+          <t xml:space="preserve">9198
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118
-</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">484
+          <t xml:space="preserve">1488
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3840,8 +3810,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
-</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -3864,8 +3833,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>459</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -3876,7 +3844,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3911,7 +3879,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">695
+          <t xml:space="preserve">696
 </t>
         </is>
       </c>
@@ -3927,7 +3895,7 @@
 </t>
         </is>
       </c>
-      <c r="W24" s="3" t="inlineStr">
+      <c r="W24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -3935,7 +3903,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -3966,25 +3934,24 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4904
-</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
+          <t xml:space="preserve">1304
+</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>6431</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3994,9 +3961,9 @@
 </t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -4006,34 +3973,33 @@
 </t>
         </is>
       </c>
-      <c r="J25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8492
+          <t xml:space="preserve">342
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -4048,27 +4014,27 @@
 </t>
         </is>
       </c>
-      <c r="Q25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">019
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">729
+</t>
+        </is>
+      </c>
+      <c r="S25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">681
 </t>
         </is>
       </c>
@@ -4080,13 +4046,12 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
+          <t>166</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -4123,7 +4088,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
@@ -4153,31 +4118,31 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 5
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">59
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -4201,13 +4166,13 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -4237,17 +4202,17 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="X26" s="8" t="inlineStr">
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -4255,14 +4220,12 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4280,7 +4243,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23059
+          <t xml:space="preserve">059
 </t>
         </is>
       </c>
@@ -4292,115 +4255,113 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4437,7 +4398,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20239
+          <t xml:space="preserve">3059
 </t>
         </is>
       </c>
@@ -4453,10 +4414,9 @@
 </t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1179
-</t>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>119</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -4467,31 +4427,31 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">654
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -4503,7 +4463,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -4514,7 +4474,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4544,7 +4504,7 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
@@ -4596,7 +4556,7 @@
 </t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">219
 </t>
@@ -4610,14 +4570,13 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -4628,7 +4587,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4640,11 +4599,11 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
+          <t xml:space="preserve">67
+</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">149
 </t>
@@ -4652,13 +4611,13 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4670,8 +4629,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -4694,7 +4652,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">700
+          <t xml:space="preserve">709
 </t>
         </is>
       </c>
@@ -4749,19 +4707,19 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16829
+          <t xml:space="preserve">16899
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11209
+          <t xml:space="preserve">11298
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
+          <t xml:space="preserve">606
 </t>
         </is>
       </c>
@@ -4785,7 +4743,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -4797,7 +4755,8 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t xml:space="preserve">386
+</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -4808,36 +4767,36 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>718</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200214
+          <t xml:space="preserve">4798
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -4849,7 +4808,7 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5619
+          <t xml:space="preserve">5618
 </t>
         </is>
       </c>
@@ -4861,31 +4820,31 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">880
 </t>
         </is>
       </c>
-      <c r="W30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">811
-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4418
+          <t xml:space="preserve">4 16 8
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -4910,7 +4869,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4934,7 +4893,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -4946,13 +4905,13 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1 8
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">386
 </t>
         </is>
       </c>
@@ -4964,13 +4923,13 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -5006,13 +4965,12 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -5036,13 +4994,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5060,7 +5018,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4828
+          <t xml:space="preserve">4818
 </t>
         </is>
       </c>
@@ -5072,19 +5030,19 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">719
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5096,61 +5054,60 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="M32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>1051</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8950
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -5162,7 +5119,7 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9011
+          <t xml:space="preserve">901
 </t>
         </is>
       </c>
@@ -5174,13 +5131,13 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="W32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -5217,43 +5174,43 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4828
-</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">4228
+</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">491
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">66184 5
+</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -5264,13 +5221,14 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">161
+</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -5279,9 +5237,9 @@
 </t>
         </is>
       </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -5293,7 +5251,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -5311,17 +5269,17 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
+          <t xml:space="preserve">3195
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">144
 </t>
@@ -5335,19 +5293,19 @@
       </c>
       <c r="W33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
-</t>
-        </is>
-      </c>
-      <c r="X33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">406
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
@@ -5376,21 +5334,20 @@
 </t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">250
 </t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1136
-</t>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5400,27 +5357,26 @@
 </t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">083
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5432,13 +5388,13 @@
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
@@ -5450,7 +5406,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5462,7 +5418,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -5474,7 +5430,7 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
@@ -5492,16 +5448,11 @@
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="n"/>
       <c r="Y34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">210
@@ -5510,7 +5461,7 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
@@ -5529,13 +5480,13 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -5547,8 +5498,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -5576,7 +5526,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5586,72 +5536,73 @@
 </t>
         </is>
       </c>
-      <c r="M35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">17
 </t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91800
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="Q35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6008
-</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14248
-</t>
-        </is>
-      </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="W35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="X35" s="8" t="inlineStr">
+      <c r="X35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">185
 </t>
@@ -5700,13 +5651,13 @@
 </t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
+</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">103
 </t>
@@ -5714,12 +5665,12 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5747,9 +5698,9 @@
 </t>
         </is>
       </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+      <c r="N36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
@@ -5765,9 +5716,9 @@
 </t>
         </is>
       </c>
-      <c r="Q36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1242
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -5777,21 +5728,21 @@
 </t>
         </is>
       </c>
-      <c r="S36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">710
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521
-</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14248
+          <t xml:space="preserve">551
+</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5840,86 +5791,84 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8258
+          <t xml:space="preserve">698
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">040
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">831
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80120
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490
-</t>
+          <t>449303</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5930,13 +5879,13 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5948,13 +5897,13 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -5966,19 +5915,18 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9402
-</t>
+          <t>412524</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -5997,7 +5945,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94386
+          <t xml:space="preserve">4386
 </t>
         </is>
       </c>
@@ -6021,34 +5969,34 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="K38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">151
 </t>
@@ -6062,19 +6010,18 @@
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">581
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>898</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6092,14 +6039,12 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">621
-</t>
+          <t>639</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
@@ -6116,7 +6061,7 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
@@ -6128,13 +6073,13 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2249
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 0
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -6153,19 +6098,19 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3950
-</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">645
+          <t xml:space="preserve">23923
+</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -6177,19 +6122,19 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -6201,25 +6146,25 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">015
 </t>
         </is>
       </c>
@@ -6235,9 +6180,9 @@
 </t>
         </is>
       </c>
-      <c r="Q39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
@@ -6249,49 +6194,49 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">520
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">710
 </t>
         </is>
       </c>
-      <c r="W39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -6316,116 +6261,110 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">492
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">016
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">806
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="n"/>
+      <c r="K40" s="3" t="n"/>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="K40" s="3" t="n"/>
-      <c r="L40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="M40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">588
+</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
 </t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2995
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">685
-</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -6472,7 +6411,7 @@
 </t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">125
 </t>
@@ -6484,9 +6423,9 @@
 </t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -6498,7 +6437,7 @@
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -6522,14 +6461,14 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -6539,15 +6478,15 @@
 </t>
         </is>
       </c>
-      <c r="Q41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1239
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -6559,24 +6498,25 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1625
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t>09</t>
+          <t xml:space="preserve">10
+</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="W41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -6594,7 +6534,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -6613,11 +6553,11 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3491
-</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
+          <t xml:space="preserve">3401
+</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">224
 </t>
@@ -6625,7 +6565,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -6636,13 +6576,18 @@
         </is>
       </c>
       <c r="G42" s="3" t="n"/>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">137
 </t>
         </is>
       </c>
-      <c r="I42" s="3" t="n"/>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">40
@@ -6657,13 +6602,13 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -6687,13 +6632,13 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">434
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -6705,7 +6650,7 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14605
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
@@ -6755,13 +6700,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5170
+          <t xml:space="preserve">5370
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>495</t>
         </is>
       </c>
       <c r="E43" s="3" t="n"/>
@@ -6771,34 +6716,33 @@
 </t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 18
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
@@ -6809,18 +6753,19 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">151
+</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -6836,9 +6781,9 @@
 </t>
         </is>
       </c>
-      <c r="R43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -6850,13 +6795,13 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
@@ -6867,7 +6812,7 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -6903,7 +6848,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6531
+          <t xml:space="preserve">2231
 </t>
         </is>
       </c>
@@ -6952,8 +6897,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -6971,7 +6915,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -6983,7 +6927,7 @@
       </c>
       <c r="R44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">681
+          <t xml:space="preserve">671
 </t>
         </is>
       </c>
@@ -7000,7 +6944,7 @@
         </is>
       </c>
       <c r="U44" s="3" t="n"/>
-      <c r="V44" s="3" t="inlineStr">
+      <c r="V44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">181
 </t>
@@ -7025,144 +6969,144 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22830
+          <t xml:space="preserve">22820
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1985
+          <t xml:space="preserve">19818
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2191
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">2862
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1801
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">070
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2909
+          <t xml:space="preserve">2409
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3810
+          <t xml:space="preserve">3310
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2208
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>46484</t>
+          <t xml:space="preserve">9668
+</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -7181,7 +7125,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4980
+          <t xml:space="preserve">4970
 </t>
         </is>
       </c>
@@ -7193,7 +7137,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -7227,39 +7171,34 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
+      <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">149
 </t>
         </is>
       </c>
-      <c r="M46" s="8" t="inlineStr">
+      <c r="M46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">138
 </t>
         </is>
       </c>
-      <c r="N46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">389
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2541
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -7287,25 +7226,20 @@
 </t>
         </is>
       </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
+      <c r="U46" s="3" t="n"/>
       <c r="V46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="W46" s="8" t="inlineStr">
+      <c r="W46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">159
 </t>
         </is>
       </c>
-      <c r="X46" s="8" t="inlineStr">
+      <c r="X46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
@@ -7313,7 +7247,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,13 +737,14 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5822
+          <t xml:space="preserve">585
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -778,19 +779,19 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -800,9 +801,9 @@
 </t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
@@ -838,23 +839,23 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="n"/>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10 7 1
-</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="n"/>
       <c r="X4" s="3" t="n"/>
       <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
@@ -873,13 +874,13 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3885
+          <t xml:space="preserve">388
 </t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">939
 </t>
         </is>
       </c>
@@ -901,56 +902,57 @@
 </t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">535
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">121
 </t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">999
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -962,13 +964,13 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="S5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -980,7 +982,7 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -1004,7 +1006,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">755
 </t>
         </is>
       </c>
@@ -1029,7 +1031,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089
+          <t xml:space="preserve">508
 </t>
         </is>
       </c>
@@ -1039,7 +1041,7 @@
 </t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">128
 </t>
@@ -1047,20 +1049,19 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -1077,7 +1078,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1087,21 +1088,21 @@
 </t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">309
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1131,7 +1132,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">615
 </t>
         </is>
       </c>
@@ -1155,20 +1156,19 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1196,10 +1196,15 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="3" t="n"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -1209,7 +1214,7 @@
 </t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">120
 </t>
@@ -1217,7 +1222,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1229,7 +1234,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -1245,33 +1250,39 @@
 </t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">521
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930
+          <t xml:space="preserve">524
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="n"/>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -1289,11 +1300,11 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr">
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
@@ -1307,13 +1318,13 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -1338,7 +1349,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -1368,96 +1379,111 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">640
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
-</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="X8" s="3" t="n"/>
-      <c r="Y8" s="3" t="n"/>
-      <c r="Z8" s="3" t="n"/>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1473,19 +1499,19 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22249
+          <t xml:space="preserve">2224
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">11185
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">676
 </t>
         </is>
       </c>
@@ -1497,7 +1523,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
@@ -1507,10 +1533,14 @@
 </t>
         </is>
       </c>
-      <c r="I9" s="3" t="n"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>7064</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1527,19 +1557,20 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">002
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>15901</t>
+          <t xml:space="preserve">590
+</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1562,7 +1593,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -1574,40 +1605,35 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1151
+</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">940
 </t>
         </is>
       </c>
-      <c r="W9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
-</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8481
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
+      <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1623,7 +1649,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4950
+          <t xml:space="preserve">445
 </t>
         </is>
       </c>
@@ -1639,7 +1665,7 @@
 </t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
@@ -1659,22 +1685,17 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">97 9
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">147
@@ -1695,19 +1716,19 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9218
+          <t xml:space="preserve">998
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 3 8
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -1717,15 +1738,15 @@
 </t>
         </is>
       </c>
-      <c r="S10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">782
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -1735,7 +1756,7 @@
 </t>
         </is>
       </c>
-      <c r="V10" s="3" t="inlineStr">
+      <c r="V10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
@@ -1755,13 +1776,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1780,12 +1801,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -1795,7 +1816,7 @@
 </t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">181
 </t>
@@ -1803,19 +1824,18 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1827,48 +1847,48 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>8850</t>
+          <t xml:space="preserve">889
+</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1880,41 +1900,45 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1406491
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>551</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">341
+</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">817
+</t>
+        </is>
+      </c>
+      <c r="X11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7175
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="n"/>
+          <t xml:space="preserve">804940
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1930,7 +1954,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290
+          <t xml:space="preserve">2295
 </t>
         </is>
       </c>
@@ -1942,7 +1966,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -1954,7 +1978,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -1982,27 +2006,27 @@
 </t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">385
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">9318
 </t>
         </is>
       </c>
@@ -2024,7 +2048,7 @@
 </t>
         </is>
       </c>
-      <c r="S12" s="3" t="inlineStr">
+      <c r="S12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">177
 </t>
@@ -2032,43 +2056,31 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="n"/>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="n"/>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2117,7 +2129,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -2141,7 +2153,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -2153,73 +2165,73 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">925
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">169
 </t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">945
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
+      <c r="W13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="W13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
@@ -2250,11 +2262,11 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">134
 </t>
@@ -2262,7 +2274,8 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -2273,12 +2286,13 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2290,7 +2304,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
@@ -2308,12 +2322,13 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>154</t>
+          <t xml:space="preserve">158
+</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">001
 </t>
         </is>
       </c>
@@ -2325,7 +2340,8 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">217
+</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
@@ -2336,35 +2352,35 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">719
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">715
-</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">174
 </t>
@@ -2372,7 +2388,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -2401,7 +2417,12 @@
 </t>
         </is>
       </c>
-      <c r="D15" s="3" t="n"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">132
@@ -2410,7 +2431,8 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2421,31 +2443,31 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 2
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -2463,13 +2485,13 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">0911
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2499,37 +2521,37 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">62
 </t>
         </is>
       </c>
-      <c r="V15" s="3" t="inlineStr">
+      <c r="Y15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
         </is>
       </c>
-      <c r="W15" s="3" t="inlineStr">
+      <c r="Z15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2548,7 +2570,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19732
+          <t xml:space="preserve">1475
 </t>
         </is>
       </c>
@@ -2560,42 +2582,41 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">644
+          <t xml:space="preserve">1644
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">460
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
@@ -2607,62 +2628,64 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>154</t>
+          <t xml:space="preserve">11404
+</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">60
+</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">069
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>614</t>
+          <t xml:space="preserve">830
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>39452</t>
+          <t xml:space="preserve">3945
+</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
@@ -2674,13 +2697,13 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4288
+          <t xml:space="preserve">12088
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -2699,29 +2722,31 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>14694</t>
+          <t xml:space="preserve">2950
+</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">088
+</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -2739,13 +2764,13 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">460
+          <t xml:space="preserve">28 14
+</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">695
 </t>
         </is>
       </c>
@@ -2757,70 +2782,70 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">929
 </t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">789
-</t>
-        </is>
-      </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">50
 </t>
         </is>
       </c>
-      <c r="V17" s="3" t="inlineStr">
+      <c r="W17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">169
 </t>
         </is>
       </c>
-      <c r="W17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">172
@@ -2829,14 +2854,13 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2854,7 +2878,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4288
+          <t xml:space="preserve">4283
 </t>
         </is>
       </c>
@@ -2866,111 +2890,103 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="n"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
-</t>
+          <t>691</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="inlineStr">
+          <t>185</t>
+        </is>
+      </c>
+      <c r="W18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">160
 </t>
@@ -2978,19 +2994,18 @@
       </c>
       <c r="X18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">701
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -3015,7 +3030,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -3031,9 +3046,9 @@
 </t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -3045,7 +3060,8 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -3060,7 +3076,7 @@
 </t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="L19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">151
 </t>
@@ -3074,7 +3090,8 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>464</t>
+          <t xml:space="preserve">155
+</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -3085,13 +3102,13 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -3121,18 +3138,19 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1853
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3144,7 +3162,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -3169,11 +3187,11 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">138
 </t>
@@ -3181,13 +3199,13 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -3199,13 +3217,12 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -3215,21 +3232,20 @@
 </t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>454</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3241,19 +3257,19 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -3271,11 +3287,11 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">176
 </t>
@@ -3283,7 +3299,8 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>755</t>
+          <t xml:space="preserve">168
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
@@ -3325,7 +3342,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -3343,13 +3360,13 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -3371,9 +3388,9 @@
 </t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">562
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -3385,12 +3402,13 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t xml:space="preserve">117
+</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">998
 </t>
         </is>
       </c>
@@ -3400,9 +3418,9 @@
 </t>
         </is>
       </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -3414,7 +3432,8 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>0431</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
@@ -3429,9 +3448,9 @@
 </t>
         </is>
       </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -3443,13 +3462,13 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8809
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -3486,7 +3505,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -3498,11 +3517,11 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">134
 </t>
@@ -3516,7 +3535,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3528,25 +3547,25 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="N22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
@@ -3568,7 +3587,7 @@
 </t>
         </is>
       </c>
-      <c r="S22" s="8" t="inlineStr">
+      <c r="S22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
@@ -3576,7 +3595,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7408
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -3588,7 +3607,7 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -3606,13 +3625,12 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
-</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -3631,7 +3649,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3642,32 +3660,29 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>26540</t>
+          <t xml:space="preserve">943
+</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>6364</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">612
+</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">99
@@ -3676,35 +3691,35 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>304</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
@@ -3716,7 +3731,8 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>888</t>
+          <t xml:space="preserve">888
+</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -3739,30 +3755,30 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9198
+          <t xml:space="preserve">919
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
+          <t xml:space="preserve">9295
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3796,7 +3812,7 @@
 </t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">183
 </t>
@@ -3810,7 +3826,8 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -3827,30 +3844,31 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0434
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">2211
 </t>
         </is>
       </c>
@@ -3868,7 +3886,8 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>478</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -3889,13 +3908,13 @@
 </t>
         </is>
       </c>
-      <c r="V24" s="3" t="inlineStr">
+      <c r="V24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">183
 </t>
         </is>
       </c>
-      <c r="W24" s="8" t="inlineStr">
+      <c r="W24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -3903,7 +3922,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3934,7 +3953,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3944,12 +3963,13 @@
 </t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>6431</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
@@ -3957,26 +3977,22 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -3987,66 +4003,61 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
+          <t xml:space="preserve">842
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9108
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">915
+</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="n"/>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">729
-</t>
-        </is>
-      </c>
-      <c r="S25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">681
-</t>
+          <t>495</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -4057,8 +4068,7 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -4069,7 +4079,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -4088,25 +4098,25 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4124,7 +4134,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4136,19 +4146,19 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">846
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4166,7 +4176,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4176,9 +4186,9 @@
 </t>
         </is>
       </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088
 </t>
         </is>
       </c>
@@ -4212,7 +4222,7 @@
 </t>
         </is>
       </c>
-      <c r="X26" s="3" t="inlineStr">
+      <c r="X26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -4220,12 +4230,14 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t xml:space="preserve">885
+</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4243,25 +4255,26 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">059
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -4272,63 +4285,59 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">12
 </t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="Q27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">179
@@ -4343,13 +4352,13 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">7170
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4361,7 +4370,7 @@
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4398,13 +4407,13 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3059
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4416,7 +4425,8 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -4427,35 +4437,35 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">142
 </t>
@@ -4463,7 +4473,8 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -4480,7 +4491,7 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -4492,8 +4503,7 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>415</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
@@ -4504,7 +4514,8 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
@@ -4533,7 +4544,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -4570,113 +4581,115 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">171
 </t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">67
-</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">844
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="T29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">709
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="V29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="W29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
+      <c r="X29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -4707,7 +4720,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16899
+          <t xml:space="preserve">16099
 </t>
         </is>
       </c>
@@ -4717,12 +4730,7 @@
 </t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">606
-</t>
-        </is>
-      </c>
+      <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">906
@@ -4731,13 +4739,12 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>497</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">866
 </t>
         </is>
       </c>
@@ -4749,7 +4756,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -4759,12 +4766,7 @@
 </t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
+      <c r="L30" s="3" t="n"/>
       <c r="M30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">117
@@ -4773,30 +4775,29 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4798
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t xml:space="preserve">1052
+</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
@@ -4808,19 +4809,19 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618
+          <t xml:space="preserve">5610
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3946
+          <t xml:space="preserve">345
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -4832,13 +4833,13 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 16 8
+          <t xml:space="preserve">4410
 </t>
         </is>
       </c>
@@ -4869,7 +4870,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -4893,7 +4894,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -4905,102 +4906,94 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">386
-</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
       <c r="M31" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">14
 </t>
         </is>
       </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">941
-</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t>1163</t>
-        </is>
-      </c>
-      <c r="U31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="V31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="W31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">2144
+</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5018,61 +5011,55 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4818
-</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -5081,9 +5068,9 @@
           <t>1051</t>
         </is>
       </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">161
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5105,57 +5092,57 @@
 </t>
         </is>
       </c>
-      <c r="R32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="T32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">901
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -5174,43 +5161,44 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4228
-</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">491
+          <t xml:space="preserve">14828
+</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66184 5
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">917
-</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -5221,13 +5209,13 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -5239,7 +5227,7 @@
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -5251,7 +5239,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5275,7 +5263,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3195
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -5285,21 +5273,21 @@
 </t>
         </is>
       </c>
-      <c r="V33" s="3" t="inlineStr">
+      <c r="V33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="W33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="X33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -5330,48 +5318,49 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4928
-</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">4828
+</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1095
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -5388,13 +5377,13 @@
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -5418,7 +5407,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -5448,23 +5437,23 @@
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="n"/>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
         </is>
       </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
+      <c r="Z34" s="3" t="n"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -5480,13 +5469,13 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">94928
+</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -5498,24 +5487,24 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">894
-</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>2793</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>446</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -5538,19 +5527,19 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">9100
 </t>
         </is>
       </c>
@@ -5560,9 +5549,9 @@
 </t>
         </is>
       </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
+      <c r="Q35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">945
 </t>
         </is>
       </c>
@@ -5580,13 +5569,13 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">6008
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5598,19 +5587,19 @@
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="X35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">755
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
@@ -5635,42 +5624,43 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4983
-</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
+          <t xml:space="preserve">94989
+</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">942
+</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">139
 </t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">921
-</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4103
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -5686,9 +5676,9 @@
 </t>
         </is>
       </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">866
 </t>
         </is>
       </c>
@@ -5700,7 +5690,7 @@
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -5716,9 +5706,9 @@
 </t>
         </is>
       </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
+      <c r="Q36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
@@ -5730,19 +5720,19 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">551
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -5758,9 +5748,9 @@
 </t>
         </is>
       </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
+      <c r="X36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666
 </t>
         </is>
       </c>
@@ -5772,7 +5762,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -5791,84 +5781,78 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">21928
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1191
+</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>6657</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">533
+</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1106
+</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">121
 </t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">698
-</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
-</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1106
-</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">757
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">7112
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">716
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>449303</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">88
+</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5885,7 +5869,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -5897,7 +5881,7 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">2348
 </t>
         </is>
       </c>
@@ -5909,25 +5893,25 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">804
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>412524</t>
+          <t xml:space="preserve">4098
+</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5945,7 +5929,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
+          <t xml:space="preserve">438
 </t>
         </is>
       </c>
@@ -5957,7 +5941,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -5969,18 +5953,19 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t xml:space="preserve">108
+</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -5990,16 +5975,10 @@
 </t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -6008,15 +5987,16 @@
 </t>
         </is>
       </c>
-      <c r="N38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">581
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>898</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -6039,12 +6019,14 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>639</t>
+          <t xml:space="preserve">827
+</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
@@ -6061,7 +6043,7 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -6073,13 +6055,13 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
@@ -6098,19 +6080,19 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23923
+          <t xml:space="preserve">395953
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -6120,9 +6102,9 @@
 </t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -6134,55 +6116,49 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">016
+</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="N39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">015
-</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -6192,9 +6168,9 @@
 </t>
         </is>
       </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
+      <c r="S39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -6206,23 +6182,17 @@
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="n"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="inlineStr">
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="X39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">158
 </t>
@@ -6230,14 +6200,12 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>641</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6255,47 +6223,55 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29421
-</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">492
+          <t>5454</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">191
+</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="n"/>
-      <c r="K40" s="3" t="n"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">008
+</t>
+        </is>
+      </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">160
@@ -6304,85 +6280,85 @@
       </c>
       <c r="M40" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">588
+</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">120
 </t>
         </is>
       </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">588
-</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
 </t>
         </is>
       </c>
-      <c r="W40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
+      <c r="W40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">4084
 </t>
         </is>
       </c>
@@ -6401,11 +6377,11 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4084
-</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
+          <t xml:space="preserve">3401
+</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">237
 </t>
@@ -6413,37 +6389,37 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">810
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -6461,14 +6437,19 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="n"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
@@ -6480,31 +6461,31 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="S41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">622
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -6516,25 +6497,25 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -6553,74 +6534,79 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3401
+          <t xml:space="preserve">3310
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -6632,13 +6618,13 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -6662,26 +6648,31 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="n"/>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -6700,78 +6691,85 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5370
+          <t xml:space="preserve">5571
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n"/>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 18
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>07</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="M43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6783,53 +6781,55 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1867
+</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="W43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6848,112 +6848,148 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2231
-</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
+          <t xml:space="preserve">29830
+</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">417
+</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">911
+</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">620
+</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">836
+</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="n"/>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="P44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3409
 </t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="R44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">671
+          <t xml:space="preserve">024
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
-</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="n"/>
+          <t xml:space="preserve">3510
+</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">690
+</t>
+        </is>
+      </c>
       <c r="V44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" s="3" t="n"/>
-      <c r="Y44" s="3" t="n"/>
-      <c r="Z44" s="3" t="n"/>
+          <t xml:space="preserve">1115
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">955
+</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">996
+</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4668
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -6969,144 +7005,144 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22820
+          <t xml:space="preserve">4970
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19818
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">894
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">006
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">152
 </t>
         </is>
       </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2862
-</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1801
-</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">899
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">070
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">313
-</t>
-        </is>
-      </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">9228
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
+          <t xml:space="preserve">585
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>360</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9668
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">448
 </t>
         </is>
       </c>
@@ -7131,129 +7167,139 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">14 5 9
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="N46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">901
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">585
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="n"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14 140
+</t>
+        </is>
+      </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1 17 5
+</t>
+        </is>
+      </c>
+      <c r="W46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111511
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,122 +737,102 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="N4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
-</t>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>145</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>207</t>
         </is>
       </c>
       <c r="W4" s="3" t="n"/>
@@ -874,146 +854,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
-</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">939
-</t>
+          <t>3883</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>237</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">535
-</t>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>135</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">755
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1031,144 +987,122 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
-</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>239</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">615
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1186,146 +1120,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5129
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>403</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">524
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">591
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="W7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1343,145 +1253,122 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2298
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>931</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
+          <t>509</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>631</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>511</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>734</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>664</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>160</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1499,141 +1386,124 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2224
-</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11185
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">676
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">931
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>9 21</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
-</t>
+          <t>511</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">734
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">002
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
-</t>
+          <t>664</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>897</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="n"/>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1649,141 +1519,122 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">445
-</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97 9
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>188</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1806,26 +1657,22 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1835,44 +1682,37 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -1882,26 +1722,22 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406491
-</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1909,36 +1745,11 @@
           <t>551</t>
         </is>
       </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">341
-</t>
-        </is>
-      </c>
-      <c r="W11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">817
-</t>
-        </is>
-      </c>
-      <c r="X11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7175
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">804940
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
+      <c r="V11" s="3" t="n"/>
+      <c r="W11" s="3" t="n"/>
+      <c r="X11" s="3" t="n"/>
+      <c r="Y11" s="3" t="n"/>
+      <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1954,110 +1765,92 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2295
-</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>130</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">839
-</t>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>135</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9318
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="S12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>177</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="U12" s="3" t="n"/>
@@ -2069,8 +1862,7 @@
       <c r="W12" s="3" t="n"/>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -2080,8 +1872,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2099,146 +1890,122 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>945</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>158</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2256,146 +2023,122 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3240
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
-</t>
+          <t>949</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
-</t>
+          <t>905</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>719</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2413,146 +2156,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3079
-</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0911
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2570,14 +2289,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1475
-</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -2587,20 +2304,17 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>474</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1644
-</t>
+          <t>644</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2610,20 +2324,17 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
-</t>
+          <t>465</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -2633,20 +2344,17 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11404
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -2656,8 +2364,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -2667,44 +2374,37 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3945
-</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
-</t>
+          <t>843</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
-</t>
+          <t>786</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
-</t>
+          <t>861</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12088
-</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2722,140 +2422,117 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2950
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28 14
-</t>
-        </is>
-      </c>
-      <c r="K17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">695
-</t>
+          <t>12 14</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>222</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>929</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>789</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -2878,26 +2555,22 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4283
-</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2905,22 +2578,19 @@
           <t>484</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>109</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2930,26 +2600,22 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>130</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P18" s="3" t="n"/>
@@ -2958,16 +2624,14 @@
           <t>46</t>
         </is>
       </c>
-      <c r="R18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>178</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -2977,8 +2641,7 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
@@ -2986,16 +2649,14 @@
           <t>185</t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">701
-</t>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>170</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -3005,8 +2666,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3024,146 +2684,122 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4406
-</t>
+          <t>406</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>140</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
-</t>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>249</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>172</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3181,38 +2817,32 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>138</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -3222,20 +2852,17 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -3245,80 +2872,67 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3336,146 +2950,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
-</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
+          <t>908</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>214</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3493,134 +3083,112 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>134</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -3630,8 +3198,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3654,39 +3221,33 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
-</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3696,14 +3257,12 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -3713,50 +3272,42 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1090
-</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>905</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3479
-</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">406
-</t>
+          <t>406</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>913</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
@@ -3771,14 +3322,12 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9295
-</t>
+          <t>355</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3796,146 +3345,122 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2154
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="M24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0434
-</t>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>144</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>183</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3953,26 +3478,22 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>178</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -3997,51 +3518,43 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">842
-</t>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>142</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
+          <t>915</t>
         </is>
       </c>
       <c r="P25" s="3" t="n"/>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="R25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
@@ -4056,14 +3569,12 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
@@ -4073,14 +3584,12 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4098,146 +3607,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">846
-</t>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>146</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="R26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">088
-</t>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>172</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="X26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>180</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4255,141 +3740,118 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>144</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>154</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>208</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7170
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4407,98 +3869,82 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="K28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>154</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>142</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -4508,44 +3954,37 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
-</t>
+          <t>728</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4563,146 +4002,122 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898
-</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>149</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>700</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="X29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4720,21 +4135,18 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16099
-</t>
+          <t>16099</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11298
-</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>906</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -4744,39 +4156,33 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
-</t>
+          <t>666</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">386
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="L30" s="3" t="n"/>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>717</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4791,62 +4197,52 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5610
-</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
-</t>
+          <t>346</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4410
-</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4864,136 +4260,114 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="n"/>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>941</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2144
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5011,33 +4385,28 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -5047,20 +4416,17 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -5068,82 +4434,69 @@
           <t>1051</t>
         </is>
       </c>
-      <c r="N32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>122</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5161,146 +4514,122 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14828
-</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">826
-</t>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>206</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="N33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">848
-</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>515</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>180</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="X33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>160</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5318,14 +4647,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4828
-</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">441
-</t>
+          <t>4828</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>241</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -5335,122 +4662,102 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1095
-</t>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>192</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="M34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>196</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>568</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Z34" s="3" t="n"/>
@@ -5469,32 +4776,27 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94928
-</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>136</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -5509,104 +4811,87 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">945
-</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>245</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6008
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="X35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
-</t>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>755</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5624,146 +4909,122 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94989
-</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">942
-</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
+          <t>989</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>139</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4103
-</t>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>103</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">866
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="N36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>182</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">881
-</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>242</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
+          <t>551</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="X36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666
-</t>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5781,14 +5042,12 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21928
-</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -5803,110 +5062,89 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">533
-</t>
+          <t>533</t>
         </is>
       </c>
       <c r="H37" s="3" t="n"/>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">757
-</t>
+          <t>757</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7112
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">716
-</t>
-        </is>
-      </c>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>44203</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2348
-</t>
+          <t>548</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
-</t>
+          <t>804</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4098
-</t>
+          <t>095</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
@@ -5929,50 +5167,42 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">438
-</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
@@ -5983,86 +5213,72 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
-</t>
+          <t>627</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>819</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>898</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6080,69 +5296,54 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">395953
-</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="M39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
-</t>
+          <t>016</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -6152,32 +5353,27 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="S39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
@@ -6188,14 +5384,12 @@
       <c r="V39" s="3" t="n"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="X39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>158</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -6228,32 +5422,27 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -6268,98 +5457,82 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="M40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="W40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>160</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4084
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6377,146 +5550,122 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3401
-</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
+          <t>4084</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>237</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>108</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>889</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="S41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t>178</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
-</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6534,146 +5683,122 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
-</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6691,146 +5816,122 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571
-</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">996
-</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>114</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="M43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">354
-</t>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1867
-</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>112</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="W43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>158</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6848,146 +5949,118 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29830
-</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">417
-</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">911
-</t>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>126</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="L44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">836
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>142</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="P44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3409
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="R44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">024
-</t>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="n"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>167</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3510
-</t>
+          <t>595</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
-</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1115
-</t>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>181</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4668
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
@@ -7005,145 +6078,122 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4970
-</t>
+          <t>29830</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>708</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>919</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9228
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>690</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>959</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7161,146 +6211,122 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4970
-</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 5 9
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="N46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>152</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 140
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 17 5
-</t>
-        </is>
-      </c>
-      <c r="W46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111511
-</t>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>159</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>554</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>270</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>220</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>173</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1120,69 +1120,69 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
+          <t>2296</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
           <t>08</t>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>601</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>9 21</t>
+          <t>22 95</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>102</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>153</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>226</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -1862,7 +1862,7 @@
       <c r="W12" s="3" t="n"/>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>715</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>960</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
@@ -2289,12 +2289,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>463</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -2344,12 +2344,12 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>145</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>832</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2422,22 +2422,22 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2457,12 +2457,12 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>12 14</t>
+          <t>0 14</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>102</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2477,12 +2477,12 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>021</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>154</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>180</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>190</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>199</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>22</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>162</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>220</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>912</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>613</t>
         </is>
       </c>
       <c r="I23" s="3" t="n"/>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>903</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>160</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>929</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>157</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>173</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>338</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>212</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>217</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>792</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>878</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>181 1</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>723</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>112</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>222</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>14828</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>266</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>140</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>193</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>167</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>176</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>172</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>790</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>21928</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>853</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>095</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>152</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -5324,7 +5324,11 @@
           <t>120</t>
         </is>
       </c>
-      <c r="I39" s="3" t="n"/>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
@@ -5333,12 +5337,12 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>288</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>115</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -5422,7 +5426,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -5437,7 +5441,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -5472,7 +5476,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5522,7 +5526,7 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>162</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -5560,7 +5564,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -5640,7 +5644,7 @@
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
@@ -5650,7 +5654,7 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
@@ -5693,7 +5697,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -5733,7 +5737,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>226</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -5788,12 +5792,12 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
@@ -5871,7 +5875,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>162</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -5911,12 +5915,12 @@
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>172</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>152</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -5949,7 +5953,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -6004,7 +6008,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -6025,7 +6029,7 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
@@ -6088,7 +6092,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -6133,7 +6137,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>918</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -6148,7 +6152,7 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>137</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
@@ -6178,7 +6182,7 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>222</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
@@ -6188,7 +6192,7 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
@@ -6231,7 +6235,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -6251,7 +6255,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6261,7 +6265,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>080</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -6316,12 +6320,12 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>114</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>585</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>388</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>155</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>185</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>224</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>681</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>164</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>22 95</t>
+          <t>2 25</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>164</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>212</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>02</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>152</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>20</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>130</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>912</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>835</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>248</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>230</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>202</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2477,12 +2477,12 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>021</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>155</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>80</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>170</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>207</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>178</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>54</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>155</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>165</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>913</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3241,13 +3241,13 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>643</t>
         </is>
       </c>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>913</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -3884,69 +3884,69 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
           <t>415</t>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>838</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="E30" s="3" t="n"/>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>361</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>05</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>181 1</t>
+          <t>181 2</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>22</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>14828</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>286</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>133</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -5324,11 +5324,7 @@
           <t>120</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
@@ -5337,17 +5333,17 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>301</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -5441,7 +5437,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -5476,7 +5472,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5526,12 +5522,12 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>720</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
@@ -5564,7 +5560,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -5609,7 +5605,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>198</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -5654,7 +5650,7 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
@@ -5737,7 +5733,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>133</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -5797,7 +5793,7 @@
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
@@ -5953,7 +5949,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -6008,7 +6004,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -6029,7 +6025,7 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
@@ -6082,7 +6078,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>29830</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6182,7 +6178,7 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>955</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
@@ -6255,7 +6251,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6265,7 +6261,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>080</t>
+          <t>084</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -6320,7 +6316,7 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
@@ -6330,7 +6326,7 @@
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">
